--- a/Documentation/Week 6/Booked Hours/Booked_Hours_Dhava.xlsx
+++ b/Documentation/Week 6/Booked Hours/Booked_Hours_Dhava.xlsx
@@ -5,12 +5,12 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wikha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 6/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C866E50-F36C-4AFD-851C-168B2D2F904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{2C866E50-F36C-4AFD-851C-168B2D2F904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33D3F1D3-942E-4C70-A45F-B333839DA723}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,19 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -320,6 +333,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -338,14 +359,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -779,36 +792,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -828,7 +841,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1192,22 +1205,22 @@
         <v>44798</v>
       </c>
       <c r="E15" s="5">
-        <v>0.5</v>
+        <v>0.48958333333333331</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G15" s="6">
         <f t="shared" si="0"/>
-        <v>0.99999999994179234</v>
+        <v>0.75</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="2"/>
-        <v>17.499999999883585</v>
+        <v>17.249999999941792</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="1"/>
-        <v>0.99999999994179234</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -1224,22 +1237,22 @@
         <v>44798</v>
       </c>
       <c r="E16" s="5">
-        <v>0.54166666666666663</v>
+        <v>0.53125</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G16" s="6">
         <f t="shared" si="0"/>
-        <v>0.99999999994179234</v>
+        <v>0.75</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="2"/>
-        <v>18.499999999825377</v>
+        <v>17.999999999941792</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="1"/>
-        <v>0.99999999994179234</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -1256,22 +1269,22 @@
         <v>44800</v>
       </c>
       <c r="E17" s="5">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="6">
         <f t="shared" si="0"/>
-        <v>0.99999999994179234</v>
+        <v>0.49999999988358468</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="2"/>
-        <v>19.499999999767169</v>
+        <v>18.499999999825377</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="1"/>
-        <v>0.99999999994179234</v>
+        <v>0.49999999988358468</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1512,14 +1525,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2121,14 +2134,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2617,14 +2630,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3111,18 +3124,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3136,6 +3137,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
